--- a/results_gen/outputs/test2_i10000_w8_r5.xlsx
+++ b/results_gen/outputs/test2_i10000_w8_r5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reube\Parallel-Monte-Carlo-Tree-Search-For-The-Orienteering-Problem\results_gen\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DC5A7C-BB37-4545-A82C-1476BC516700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0607BB-3E35-4CDF-B0EB-ECEE6401B2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-45" windowWidth="38640" windowHeight="21240" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="75" windowWidth="19740" windowHeight="21000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Results" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5805" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5811" uniqueCount="611">
   <si>
     <t>algorithm</t>
   </si>
@@ -1868,12 +1868,15 @@
   <si>
     <t>could be good VL has highest max but high variances</t>
   </si>
+  <si>
+    <t>average std</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1898,6 +1901,20 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1979,11 +1996,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1997,7 +2011,17 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -73352,36 +73376,36 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2" t="s">
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2" t="s">
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -73783,49 +73807,51 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Y129"/>
+  <dimension ref="A1:AD129"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2" t="s">
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2" t="s">
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2" t="s">
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
         <v>599</v>
@@ -73888,7 +73914,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -73896,14 +73922,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>236</v>
       </c>
       <c r="E4">
@@ -73930,13 +73956,17 @@
       <c r="N4">
         <v>98.284271247461902</v>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="2"/>
       <c r="Y4" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
+      <c r="AC4" s="14"/>
+      <c r="AD4" s="14" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
       <c r="B5" s="1" t="s">
         <v>38</v>
       </c>
@@ -73944,7 +73974,7 @@
         <v>220.8</v>
       </c>
       <c r="D5">
-        <v>8.6429161745327576</v>
+        <v>8.6429161745327594</v>
       </c>
       <c r="E5">
         <v>213</v>
@@ -74000,13 +74030,20 @@
       <c r="V5">
         <v>0.94809999999999994</v>
       </c>
-      <c r="X5" s="4"/>
+      <c r="X5" s="3"/>
       <c r="Y5" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
+      <c r="AC5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD5" s="14">
+        <f>(D5+D11+D17+D23+D29+D35+D41+D47+D53+D59+D65+D71+D77+D83+D89+D95+D101+D107+D113+D119+D125)/21</f>
+        <v>18.541094910488514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
       <c r="B6" s="1" t="s">
         <v>50</v>
       </c>
@@ -74070,13 +74107,20 @@
       <c r="V6">
         <v>0.93110000000000004</v>
       </c>
-      <c r="X6" s="5"/>
+      <c r="X6" s="4"/>
       <c r="Y6" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+      <c r="AC6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD6" s="14">
+        <f t="shared" ref="AD6:AD9" si="0">(D6+D12+D18+D24+D30+D36+D42+D48+D54+D60+D66+D72+D78+D84+D90+D96+D102+D108+D114+D120+D126)/21</f>
+        <v>16.541003361508793</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
       <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
@@ -74116,13 +74160,20 @@
       <c r="N7">
         <v>99.497474683058343</v>
       </c>
-      <c r="X7" s="6"/>
+      <c r="X7" s="5"/>
       <c r="Y7" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
+      <c r="AC7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD7" s="14">
+        <f t="shared" si="0"/>
+        <v>19.254549528700856</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
       <c r="B8" s="1" t="s">
         <v>44</v>
       </c>
@@ -74186,13 +74237,20 @@
       <c r="V8">
         <v>0.86360000000000003</v>
       </c>
-      <c r="X8" s="7"/>
+      <c r="X8" s="6"/>
       <c r="Y8" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="AC8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD8" s="14">
+        <f t="shared" si="0"/>
+        <v>20.823783240831215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
       <c r="B9" s="1" t="s">
         <v>56</v>
       </c>
@@ -74232,19 +74290,26 @@
       <c r="N9">
         <v>99.497474683058343</v>
       </c>
-      <c r="X9" s="8"/>
+      <c r="X9" s="7"/>
       <c r="Y9" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="AC9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD9" s="14">
+        <f t="shared" si="0"/>
+        <v>18.563540606516074</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>65</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <v>317</v>
       </c>
       <c r="E10">
@@ -74272,8 +74337,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
       <c r="B11" s="1" t="s">
         <v>38</v>
       </c>
@@ -74338,8 +74403,8 @@
         <v>0.97320000000000007</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A12" s="12"/>
       <c r="B12" s="1" t="s">
         <v>50</v>
       </c>
@@ -74404,8 +74469,8 @@
         <v>0.97340000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A13" s="12"/>
       <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
@@ -74446,8 +74511,8 @@
         <v>99.66498312203889</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A14" s="12"/>
       <c r="B14" s="1" t="s">
         <v>44</v>
       </c>
@@ -74512,8 +74577,8 @@
         <v>0.83699999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
       <c r="B15" s="1" t="s">
         <v>56</v>
       </c>
@@ -74554,14 +74619,14 @@
         <v>99.66498312203889</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>92</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="10">
         <v>316</v>
       </c>
       <c r="E16">
@@ -74590,7 +74655,7 @@
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
+      <c r="A17" s="12"/>
       <c r="B17" s="1" t="s">
         <v>38</v>
       </c>
@@ -74603,7 +74668,7 @@
       <c r="E17">
         <v>373</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <v>417</v>
       </c>
       <c r="G17">
@@ -74656,11 +74721,11 @@
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
+      <c r="A18" s="12"/>
       <c r="B18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>396.2</v>
       </c>
       <c r="D18">
@@ -74669,7 +74734,7 @@
       <c r="E18">
         <v>387</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <v>411</v>
       </c>
       <c r="G18">
@@ -74722,11 +74787,11 @@
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
+      <c r="A19" s="12"/>
       <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <v>399.8</v>
       </c>
       <c r="D19">
@@ -74735,7 +74800,7 @@
       <c r="E19">
         <v>383</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <v>409</v>
       </c>
       <c r="G19">
@@ -74764,20 +74829,20 @@
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
+      <c r="A20" s="12"/>
       <c r="B20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>377.6</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <v>27.2268250077015</v>
       </c>
       <c r="E20">
         <v>337</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="6">
         <v>404</v>
       </c>
       <c r="G20">
@@ -74830,20 +74895,20 @@
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
+      <c r="A21" s="12"/>
       <c r="B21" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>365.8</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>21.45227260688247</v>
       </c>
       <c r="E21">
         <v>337</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="6">
         <v>388</v>
       </c>
       <c r="G21">
@@ -74872,13 +74937,13 @@
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="15" t="s">
         <v>119</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="10">
         <v>282</v>
       </c>
       <c r="E22">
@@ -74907,7 +74972,7 @@
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
+      <c r="A23" s="15"/>
       <c r="B23" s="1" t="s">
         <v>38</v>
       </c>
@@ -74973,11 +75038,11 @@
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
+      <c r="A24" s="15"/>
       <c r="B24" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="2">
         <v>328.2</v>
       </c>
       <c r="D24">
@@ -75042,7 +75107,7 @@
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
+      <c r="A25" s="15"/>
       <c r="B25" s="1" t="s">
         <v>30</v>
       </c>
@@ -75084,20 +75149,20 @@
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
+      <c r="A26" s="15"/>
       <c r="B26" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C26">
         <v>301.2</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <v>25.984610830258749</v>
       </c>
       <c r="E26">
         <v>272</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="6">
         <v>342</v>
       </c>
       <c r="G26">
@@ -75150,11 +75215,11 @@
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>323.8</v>
       </c>
       <c r="D27">
@@ -75163,7 +75228,7 @@
       <c r="E27">
         <v>302</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <v>341</v>
       </c>
       <c r="G27">
@@ -75192,13 +75257,13 @@
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="15" t="s">
         <v>146</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="10">
         <v>376</v>
       </c>
       <c r="E28">
@@ -75227,7 +75292,7 @@
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
+      <c r="A29" s="15"/>
       <c r="B29" s="1" t="s">
         <v>38</v>
       </c>
@@ -75293,11 +75358,11 @@
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
+      <c r="A30" s="15"/>
       <c r="B30" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="2">
         <v>388</v>
       </c>
       <c r="D30">
@@ -75359,7 +75424,7 @@
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
+      <c r="A31" s="15"/>
       <c r="B31" s="1" t="s">
         <v>30</v>
       </c>
@@ -75401,7 +75466,7 @@
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
+      <c r="A32" s="15"/>
       <c r="B32" s="1" t="s">
         <v>44</v>
       </c>
@@ -75467,11 +75532,11 @@
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
+      <c r="A33" s="15"/>
       <c r="B33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="2">
         <v>379.6</v>
       </c>
       <c r="D33">
@@ -75509,19 +75574,19 @@
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="12" t="s">
         <v>173</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="9">
         <v>558</v>
       </c>
       <c r="E34">
         <v>558</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="11">
         <v>558</v>
       </c>
       <c r="G34">
@@ -75544,7 +75609,7 @@
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
+      <c r="A35" s="12"/>
       <c r="B35" s="1" t="s">
         <v>38</v>
       </c>
@@ -75610,7 +75675,7 @@
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
+      <c r="A36" s="12"/>
       <c r="B36" s="1" t="s">
         <v>50</v>
       </c>
@@ -75676,7 +75741,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
+      <c r="A37" s="12"/>
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
@@ -75718,7 +75783,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
+      <c r="A38" s="12"/>
       <c r="B38" s="1" t="s">
         <v>44</v>
       </c>
@@ -75784,7 +75849,7 @@
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
+      <c r="A39" s="12"/>
       <c r="B39" s="1" t="s">
         <v>56</v>
       </c>
@@ -75826,13 +75891,13 @@
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="12" t="s">
         <v>200</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="9">
         <v>260</v>
       </c>
       <c r="E40">
@@ -75861,7 +75926,7 @@
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
+      <c r="A41" s="12"/>
       <c r="B41" s="1" t="s">
         <v>38</v>
       </c>
@@ -75927,7 +75992,7 @@
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A42" s="2"/>
+      <c r="A42" s="12"/>
       <c r="B42" s="1" t="s">
         <v>50</v>
       </c>
@@ -75993,7 +76058,7 @@
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
+      <c r="A43" s="12"/>
       <c r="B43" s="1" t="s">
         <v>30</v>
       </c>
@@ -76035,7 +76100,7 @@
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A44" s="2"/>
+      <c r="A44" s="12"/>
       <c r="B44" s="1" t="s">
         <v>44</v>
       </c>
@@ -76101,7 +76166,7 @@
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
+      <c r="A45" s="12"/>
       <c r="B45" s="1" t="s">
         <v>56</v>
       </c>
@@ -76143,13 +76208,13 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="12" t="s">
         <v>227</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="10">
         <v>315</v>
       </c>
       <c r="E46">
@@ -76178,7 +76243,7 @@
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
+      <c r="A47" s="12"/>
       <c r="B47" s="1" t="s">
         <v>38</v>
       </c>
@@ -76244,11 +76309,11 @@
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
+      <c r="A48" s="12"/>
       <c r="B48" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="2">
         <v>345.4</v>
       </c>
       <c r="D48">
@@ -76257,7 +76322,7 @@
       <c r="E48">
         <v>341</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="6">
         <v>352</v>
       </c>
       <c r="G48">
@@ -76310,7 +76375,7 @@
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
+      <c r="A49" s="12"/>
       <c r="B49" s="1" t="s">
         <v>30</v>
       </c>
@@ -76352,7 +76417,7 @@
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A50" s="2"/>
+      <c r="A50" s="12"/>
       <c r="B50" s="1" t="s">
         <v>44</v>
       </c>
@@ -76418,7 +76483,7 @@
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
+      <c r="A51" s="12"/>
       <c r="B51" s="1" t="s">
         <v>56</v>
       </c>
@@ -76460,13 +76525,13 @@
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="12" t="s">
         <v>254</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="11">
+      <c r="C52" s="10">
         <v>444</v>
       </c>
       <c r="E52">
@@ -76495,7 +76560,7 @@
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
+      <c r="A53" s="12"/>
       <c r="B53" s="1" t="s">
         <v>38</v>
       </c>
@@ -76561,7 +76626,7 @@
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
+      <c r="A54" s="12"/>
       <c r="B54" s="1" t="s">
         <v>50</v>
       </c>
@@ -76627,7 +76692,7 @@
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
+      <c r="A55" s="12"/>
       <c r="B55" s="1" t="s">
         <v>30</v>
       </c>
@@ -76669,7 +76734,7 @@
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A56" s="2"/>
+      <c r="A56" s="12"/>
       <c r="B56" s="1" t="s">
         <v>44</v>
       </c>
@@ -76735,11 +76800,11 @@
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A57" s="2"/>
+      <c r="A57" s="12"/>
       <c r="B57" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="2">
         <v>446.8</v>
       </c>
       <c r="D57">
@@ -76777,13 +76842,13 @@
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="16" t="s">
         <v>280</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="10">
         <v>290</v>
       </c>
       <c r="E58">
@@ -76812,7 +76877,7 @@
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A59" s="13"/>
+      <c r="A59" s="16"/>
       <c r="B59" s="1" t="s">
         <v>38</v>
       </c>
@@ -76878,11 +76943,11 @@
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A60" s="13"/>
+      <c r="A60" s="16"/>
       <c r="B60" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="5">
         <v>305.2</v>
       </c>
       <c r="D60">
@@ -76944,7 +77009,7 @@
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A61" s="13"/>
+      <c r="A61" s="16"/>
       <c r="B61" s="1" t="s">
         <v>30</v>
       </c>
@@ -76986,7 +77051,7 @@
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A62" s="13"/>
+      <c r="A62" s="16"/>
       <c r="B62" s="1" t="s">
         <v>44</v>
       </c>
@@ -77052,11 +77117,11 @@
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A63" s="13"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="2">
         <v>309.60000000000002</v>
       </c>
       <c r="D63">
@@ -77094,13 +77159,13 @@
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="12" t="s">
         <v>305</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C64" s="9">
         <v>439</v>
       </c>
       <c r="E64">
@@ -77129,7 +77194,7 @@
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A65" s="2"/>
+      <c r="A65" s="12"/>
       <c r="B65" s="1" t="s">
         <v>38</v>
       </c>
@@ -77195,7 +77260,7 @@
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A66" s="2"/>
+      <c r="A66" s="12"/>
       <c r="B66" s="1" t="s">
         <v>50</v>
       </c>
@@ -77261,7 +77326,7 @@
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A67" s="2"/>
+      <c r="A67" s="12"/>
       <c r="B67" s="1" t="s">
         <v>30</v>
       </c>
@@ -77303,7 +77368,7 @@
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A68" s="2"/>
+      <c r="A68" s="12"/>
       <c r="B68" s="1" t="s">
         <v>44</v>
       </c>
@@ -77369,7 +77434,7 @@
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A69" s="2"/>
+      <c r="A69" s="12"/>
       <c r="B69" s="1" t="s">
         <v>56</v>
       </c>
@@ -77417,7 +77482,7 @@
       <c r="B70" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C70" s="10">
+      <c r="C70" s="9">
         <v>370</v>
       </c>
       <c r="E70">
@@ -77728,13 +77793,13 @@
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="15" t="s">
         <v>358</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C76" s="11">
+      <c r="C76" s="10">
         <v>453</v>
       </c>
       <c r="E76">
@@ -77763,7 +77828,7 @@
       </c>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
+      <c r="A77" s="15"/>
       <c r="B77" s="1" t="s">
         <v>38</v>
       </c>
@@ -77829,7 +77894,7 @@
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
+      <c r="A78" s="15"/>
       <c r="B78" s="1" t="s">
         <v>50</v>
       </c>
@@ -77895,7 +77960,7 @@
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
+      <c r="A79" s="15"/>
       <c r="B79" s="1" t="s">
         <v>30</v>
       </c>
@@ -77937,7 +78002,7 @@
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
+      <c r="A80" s="15"/>
       <c r="B80" s="1" t="s">
         <v>44</v>
       </c>
@@ -78003,11 +78068,11 @@
       </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
+      <c r="A81" s="15"/>
       <c r="B81" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C81" s="3">
+      <c r="C81" s="2">
         <v>478</v>
       </c>
       <c r="D81">
@@ -78045,13 +78110,13 @@
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="12" t="s">
         <v>385</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="8">
         <v>622</v>
       </c>
       <c r="E82">
@@ -78080,7 +78145,7 @@
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A83" s="2"/>
+      <c r="A83" s="12"/>
       <c r="B83" s="1" t="s">
         <v>38</v>
       </c>
@@ -78146,7 +78211,7 @@
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A84" s="2"/>
+      <c r="A84" s="12"/>
       <c r="B84" s="1" t="s">
         <v>50</v>
       </c>
@@ -78212,7 +78277,7 @@
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A85" s="2"/>
+      <c r="A85" s="12"/>
       <c r="B85" s="1" t="s">
         <v>30</v>
       </c>
@@ -78254,7 +78319,7 @@
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A86" s="2"/>
+      <c r="A86" s="12"/>
       <c r="B86" s="1" t="s">
         <v>44</v>
       </c>
@@ -78320,7 +78385,7 @@
       </c>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A87" s="2"/>
+      <c r="A87" s="12"/>
       <c r="B87" s="1" t="s">
         <v>56</v>
       </c>
@@ -78362,13 +78427,13 @@
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
+      <c r="A88" s="12" t="s">
         <v>411</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C88" s="8">
         <v>450</v>
       </c>
       <c r="E88">
@@ -78397,7 +78462,7 @@
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A89" s="2"/>
+      <c r="A89" s="12"/>
       <c r="B89" s="1" t="s">
         <v>38</v>
       </c>
@@ -78463,7 +78528,7 @@
       </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A90" s="2"/>
+      <c r="A90" s="12"/>
       <c r="B90" s="1" t="s">
         <v>50</v>
       </c>
@@ -78529,7 +78594,7 @@
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A91" s="2"/>
+      <c r="A91" s="12"/>
       <c r="B91" s="1" t="s">
         <v>30</v>
       </c>
@@ -78571,7 +78636,7 @@
       </c>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A92" s="2"/>
+      <c r="A92" s="12"/>
       <c r="B92" s="1" t="s">
         <v>44</v>
       </c>
@@ -78637,7 +78702,7 @@
       </c>
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A93" s="2"/>
+      <c r="A93" s="12"/>
       <c r="B93" s="1" t="s">
         <v>56</v>
       </c>
@@ -78679,13 +78744,13 @@
       </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="12" t="s">
         <v>438</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C94" s="8">
         <v>436</v>
       </c>
       <c r="E94">
@@ -78714,7 +78779,7 @@
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A95" s="2"/>
+      <c r="A95" s="12"/>
       <c r="B95" s="1" t="s">
         <v>38</v>
       </c>
@@ -78780,11 +78845,11 @@
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A96" s="2"/>
+      <c r="A96" s="12"/>
       <c r="B96" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C96" s="3">
+      <c r="C96" s="2">
         <v>341.2</v>
       </c>
       <c r="D96">
@@ -78846,7 +78911,7 @@
       </c>
     </row>
     <row r="97" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A97" s="2"/>
+      <c r="A97" s="12"/>
       <c r="B97" s="1" t="s">
         <v>30</v>
       </c>
@@ -78888,7 +78953,7 @@
       </c>
     </row>
     <row r="98" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A98" s="2"/>
+      <c r="A98" s="12"/>
       <c r="B98" s="1" t="s">
         <v>44</v>
       </c>
@@ -78954,7 +79019,7 @@
       </c>
     </row>
     <row r="99" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A99" s="2"/>
+      <c r="A99" s="12"/>
       <c r="B99" s="1" t="s">
         <v>56</v>
       </c>
@@ -78996,13 +79061,13 @@
       </c>
     </row>
     <row r="100" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="12" t="s">
         <v>465</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C100" s="10">
+      <c r="C100" s="9">
         <v>414</v>
       </c>
       <c r="E100">
@@ -79031,7 +79096,7 @@
       </c>
     </row>
     <row r="101" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A101" s="2"/>
+      <c r="A101" s="12"/>
       <c r="B101" s="1" t="s">
         <v>38</v>
       </c>
@@ -79097,7 +79162,7 @@
       </c>
     </row>
     <row r="102" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A102" s="2"/>
+      <c r="A102" s="12"/>
       <c r="B102" s="1" t="s">
         <v>50</v>
       </c>
@@ -79163,7 +79228,7 @@
       </c>
     </row>
     <row r="103" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A103" s="2"/>
+      <c r="A103" s="12"/>
       <c r="B103" s="1" t="s">
         <v>30</v>
       </c>
@@ -79205,7 +79270,7 @@
       </c>
     </row>
     <row r="104" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A104" s="2"/>
+      <c r="A104" s="12"/>
       <c r="B104" s="1" t="s">
         <v>44</v>
       </c>
@@ -79271,7 +79336,7 @@
       </c>
     </row>
     <row r="105" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A105" s="2"/>
+      <c r="A105" s="12"/>
       <c r="B105" s="1" t="s">
         <v>56</v>
       </c>
@@ -79313,13 +79378,13 @@
       </c>
     </row>
     <row r="106" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="12" t="s">
         <v>492</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C106" s="10">
+      <c r="C106" s="9">
         <v>536</v>
       </c>
       <c r="E106">
@@ -79348,7 +79413,7 @@
       </c>
     </row>
     <row r="107" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A107" s="2"/>
+      <c r="A107" s="12"/>
       <c r="B107" s="1" t="s">
         <v>38</v>
       </c>
@@ -79414,7 +79479,7 @@
       </c>
     </row>
     <row r="108" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A108" s="2"/>
+      <c r="A108" s="12"/>
       <c r="B108" s="1" t="s">
         <v>50</v>
       </c>
@@ -79480,7 +79545,7 @@
       </c>
     </row>
     <row r="109" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A109" s="2"/>
+      <c r="A109" s="12"/>
       <c r="B109" s="1" t="s">
         <v>30</v>
       </c>
@@ -79522,7 +79587,7 @@
       </c>
     </row>
     <row r="110" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A110" s="2"/>
+      <c r="A110" s="12"/>
       <c r="B110" s="1" t="s">
         <v>44</v>
       </c>
@@ -79588,7 +79653,7 @@
       </c>
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A111" s="2"/>
+      <c r="A111" s="12"/>
       <c r="B111" s="1" t="s">
         <v>56</v>
       </c>
@@ -79630,13 +79695,13 @@
       </c>
     </row>
     <row r="112" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="12" t="s">
         <v>519</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C112" s="11">
+      <c r="C112" s="10">
         <v>313</v>
       </c>
       <c r="E112">
@@ -79665,7 +79730,7 @@
       </c>
     </row>
     <row r="113" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A113" s="2"/>
+      <c r="A113" s="12"/>
       <c r="B113" s="1" t="s">
         <v>38</v>
       </c>
@@ -79731,11 +79796,11 @@
       </c>
     </row>
     <row r="114" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A114" s="2"/>
+      <c r="A114" s="12"/>
       <c r="B114" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C114" s="3">
+      <c r="C114" s="2">
         <v>366.6</v>
       </c>
       <c r="D114">
@@ -79744,7 +79809,7 @@
       <c r="E114">
         <v>324</v>
       </c>
-      <c r="F114" s="7">
+      <c r="F114" s="6">
         <v>381</v>
       </c>
       <c r="G114">
@@ -79797,7 +79862,7 @@
       </c>
     </row>
     <row r="115" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A115" s="2"/>
+      <c r="A115" s="12"/>
       <c r="B115" s="1" t="s">
         <v>30</v>
       </c>
@@ -79839,7 +79904,7 @@
       </c>
     </row>
     <row r="116" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A116" s="2"/>
+      <c r="A116" s="12"/>
       <c r="B116" s="1" t="s">
         <v>44</v>
       </c>
@@ -79905,7 +79970,7 @@
       </c>
     </row>
     <row r="117" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A117" s="2"/>
+      <c r="A117" s="12"/>
       <c r="B117" s="1" t="s">
         <v>56</v>
       </c>
@@ -79953,7 +80018,7 @@
       <c r="B118" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C118" s="11">
+      <c r="C118" s="10">
         <v>404</v>
       </c>
       <c r="E118">
@@ -80052,7 +80117,7 @@
       <c r="B120" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C120" s="5">
         <v>404.4</v>
       </c>
       <c r="D120">
@@ -80226,7 +80291,7 @@
       <c r="B123" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C123" s="3">
+      <c r="C123" s="2">
         <v>416.4</v>
       </c>
       <c r="D123">
@@ -80235,7 +80300,7 @@
       <c r="E123">
         <v>382</v>
       </c>
-      <c r="F123" s="7">
+      <c r="F123" s="6">
         <v>437</v>
       </c>
       <c r="G123">
@@ -80264,13 +80329,13 @@
       </c>
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="12" t="s">
         <v>573</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C124" s="10">
+      <c r="C124" s="9">
         <v>575</v>
       </c>
       <c r="E124">
@@ -80299,7 +80364,7 @@
       </c>
     </row>
     <row r="125" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A125" s="2"/>
+      <c r="A125" s="12"/>
       <c r="B125" s="1" t="s">
         <v>38</v>
       </c>
@@ -80365,7 +80430,7 @@
       </c>
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A126" s="2"/>
+      <c r="A126" s="12"/>
       <c r="B126" s="1" t="s">
         <v>50</v>
       </c>
@@ -80431,7 +80496,7 @@
       </c>
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A127" s="2"/>
+      <c r="A127" s="12"/>
       <c r="B127" s="1" t="s">
         <v>30</v>
       </c>
@@ -80473,7 +80538,7 @@
       </c>
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A128" s="2"/>
+      <c r="A128" s="12"/>
       <c r="B128" s="1" t="s">
         <v>44</v>
       </c>
@@ -80539,7 +80604,7 @@
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A129" s="2"/>
+      <c r="A129" s="12"/>
       <c r="B129" s="1" t="s">
         <v>56</v>
       </c>
@@ -80582,6 +80647,19 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="A94:A99"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A58:A63"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="A82:A87"/>
     <mergeCell ref="A124:A129"/>
     <mergeCell ref="A118:A123"/>
     <mergeCell ref="A46:A51"/>
@@ -80595,19 +80673,6 @@
     <mergeCell ref="A34:A39"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A94:A99"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A58:A63"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="A82:A87"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
